--- a/Images_BGA/Results Samples/Reports/PCBA2_04_inspection_report.xlsx
+++ b/Images_BGA/Results Samples/Reports/PCBA2_04_inspection_report.xlsx
@@ -40,7 +40,7 @@
     <t>Report generated</t>
   </si>
   <si>
-    <t>2026-07-09 19:56</t>
+    <t>2026-07-09 20:37</t>
   </si>
   <si>
     <t>Inspection tool</t>
@@ -70,7 +70,7 @@
     <t>Processing time</t>
   </si>
   <si>
-    <t>165.3 s</t>
+    <t>95.9 s</t>
   </si>
   <si>
     <t>IPC VERDICT:  ACCEPT WITH PROCESS INDICATORS</t>
